--- a/Modelagem/Dados produzidos/Ocorrências Literatura.xlsx
+++ b/Modelagem/Dados produzidos/Ocorrências Literatura.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cofres Obsidian\Mar Aberto\Laboratório\lagostas_carapaca\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cofres Obsidian\Mar Aberto\Laboratório\lagostas_carapaca\Modelagem\Dados produzidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BBFB1C-2FAC-448A-BBB6-16F75D7B2968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252403E3-8A1B-4779-9C8E-8421F69929CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="7830" windowWidth="16140" windowHeight="7515" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5205" yWindow="4215" windowWidth="16140" windowHeight="7515" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ocorrências Panulirus" sheetId="1" r:id="rId1"/>
